--- a/data/xlsx/c01.xlsx
+++ b/data/xlsx/c01.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/blauerbock/workspaces/dlt-pipeline/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/blauerbock/workspaces/dlt-pipeline/data/xlsx/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C40F360-7219-854B-8D80-F058AA8D64E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58A8FA42-C61A-384F-BC86-6B7958E1A670}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="400" yWindow="600" windowWidth="25440" windowHeight="15800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -70,9 +70,6 @@
     <t>Met at trade fair; follow-up needed</t>
   </si>
   <si>
-    <t>co1</t>
-  </si>
-  <si>
     <t>138-0013-8001</t>
   </si>
   <si>
@@ -116,6 +113,9 @@
   </si>
   <si>
     <t>2024.04.01</t>
+  </si>
+  <si>
+    <t>c01</t>
   </si>
 </sst>
 </file>
@@ -1006,18 +1006,18 @@
         <v>11</v>
       </c>
       <c r="H2" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" t="s">
         <v>13</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
         <v>14</v>
-      </c>
-      <c r="D3" t="s">
-        <v>15</v>
       </c>
       <c r="E3" s="1">
         <v>45306</v>
@@ -1026,21 +1026,21 @@
         <v>45342</v>
       </c>
       <c r="G3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H3" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" t="s">
         <v>17</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>18</v>
-      </c>
-      <c r="D4" t="s">
-        <v>19</v>
       </c>
       <c r="E4" s="1">
         <v>45352</v>
@@ -1049,53 +1049,53 @@
         <v>45366</v>
       </c>
       <c r="G4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H4" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" t="s">
         <v>21</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5" t="s">
         <v>22</v>
       </c>
-      <c r="D5" t="s">
-        <v>23</v>
-      </c>
       <c r="E5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H5" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C6" t="s">
         <v>24</v>
       </c>
-      <c r="C6" t="s">
+      <c r="D6" t="s">
         <v>25</v>
-      </c>
-      <c r="D6" t="s">
-        <v>26</v>
       </c>
       <c r="E6">
         <v>20240320</v>
       </c>
       <c r="F6" t="s">
+        <v>26</v>
+      </c>
+      <c r="H6" t="s">
         <v>27</v>
-      </c>
-      <c r="H6" t="s">
-        <v>12</v>
       </c>
     </row>
   </sheetData>

--- a/data/xlsx/c01.xlsx
+++ b/data/xlsx/c01.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/blauerbock/workspaces/dlt-pipeline/data/xlsx/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58A8FA42-C61A-384F-BC86-6B7958E1A670}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EBA7B28-7845-C541-9313-924A2B485284}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="400" yWindow="600" windowWidth="25440" windowHeight="15800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1100,5 +1100,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>